--- a/zib2017-2020/mapping deprecated zibs/mapping/excel/Mapping BehandelAanwijzing BehandelAanwijzing2.xlsx
+++ b/zib2017-2020/mapping deprecated zibs/mapping/excel/Mapping BehandelAanwijzing BehandelAanwijzing2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl-my.sharepoint.com/personal/wouter_zanen_nictiz_nl/Documents/Documenten/GitHub/Zibtranslate/zib2017-2020/mapping deprecated zibs/mapping/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="765" documentId="13_ncr:1_{2553158B-2B48-A74E-A5FA-9C19D0295F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46C16902-3C8C-4BF0-88B3-754CE0240128}"/>
+  <xr:revisionPtr revIDLastSave="766" documentId="13_ncr:1_{2553158B-2B48-A74E-A5FA-9C19D0295F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3792CD62-1AD9-4115-A82E-04977FF471C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="translations" sheetId="1" r:id="rId1"/>
@@ -256,9 +256,6 @@
   </si>
   <si>
     <t>ZibName 2017</t>
-  </si>
-  <si>
-    <t>Zibname 2020</t>
   </si>
   <si>
     <t>zie AfspraakPartij</t>
@@ -361,6 +358,9 @@
   </si>
   <si>
     <t>0.2.0</t>
+  </si>
+  <si>
+    <t>ZibName 2020</t>
   </si>
 </sst>
 </file>
@@ -458,7 +458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -477,7 +477,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1245,8 +1244,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9628137" y="9982210"/>
-          <a:ext cx="647412" cy="581997"/>
+          <a:off x="9909124" y="9907597"/>
+          <a:ext cx="647412" cy="577235"/>
           <a:chOff x="6670528" y="7795390"/>
           <a:chExt cx="598714" cy="592661"/>
         </a:xfrm>
@@ -2247,16 +2246,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="6" width="40.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="40.7109375" customWidth="1"/>
-    <col min="10" max="10" width="63.7109375" customWidth="1"/>
-    <col min="11" max="11" width="40.7109375" customWidth="1"/>
-    <col min="12" max="12" width="73.140625" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="6" width="40.6640625" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="40.6640625" customWidth="1"/>
+    <col min="10" max="10" width="63.6640625" customWidth="1"/>
+    <col min="11" max="11" width="40.6640625" customWidth="1"/>
+    <col min="12" max="12" width="73.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2276,7 +2275,7 @@
         <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -2288,13 +2287,13 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2334,7 +2333,7 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K3" t="s">
         <v>66</v>
@@ -2357,7 +2356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="345">
+    <row r="5" spans="1:12" ht="288">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2386,10 +2385,10 @@
         <v>67</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="74.25">
+    <row r="6" spans="1:12" ht="71.400000000000006">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2412,10 +2411,10 @@
         <v>49</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2480,7 +2479,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="150">
+    <row r="9" spans="1:12" ht="144">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2509,13 +2508,13 @@
         <v>60</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>76</v>
-      </c>
     </row>
-    <row r="10" spans="1:12" ht="30">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2538,7 +2537,7 @@
         <v>48</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>65</v>
@@ -2570,7 +2569,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="75">
+    <row r="12" spans="1:12" ht="57.6">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2593,7 +2592,7 @@
         <v>50</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K12" t="s">
         <v>65</v>
@@ -2674,7 +2673,7 @@
         <v>66</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2694,7 +2693,7 @@
         <v>66</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2714,10 +2713,10 @@
         <v>66</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="75">
+    <row r="18" spans="1:11" ht="57.6">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2740,10 +2739,10 @@
         <v>55</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2769,24 +2768,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF649400-9F04-47E5-B81E-E7F2F2907568}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="8">
+        <v>86</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
     </row>
@@ -2799,13 +2798,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD9EA8C-6979-7F49-B6F7-170A99430065}">
   <dimension ref="B32:F32"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="89.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="6" customWidth="1"/>
-    <col min="5" max="6" width="10.85546875" style="6"/>
-    <col min="7" max="16384" width="10.85546875" style="5"/>
+    <col min="1" max="1" width="89.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="6" customWidth="1"/>
+    <col min="5" max="6" width="10.88671875" style="6"/>
+    <col min="7" max="16384" width="10.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="32" ht="22.35" customHeight="1"/>

--- a/zib2017-2020/mapping deprecated zibs/mapping/excel/Mapping BehandelAanwijzing BehandelAanwijzing2.xlsx
+++ b/zib2017-2020/mapping deprecated zibs/mapping/excel/Mapping BehandelAanwijzing BehandelAanwijzing2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl-my.sharepoint.com/personal/wouter_zanen_nictiz_nl/Documents/Documenten/GitHub/Zibtranslate/zib2017-2020/mapping deprecated zibs/mapping/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl-my.sharepoint.com/personal/jacob_engel_nictiz_nl/Documents/Documenten/GitHub/Zibtranslate/zib2017-2020/mapping deprecated zibs/mapping/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="766" documentId="13_ncr:1_{2553158B-2B48-A74E-A5FA-9C19D0295F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3792CD62-1AD9-4115-A82E-04977FF471C6}"/>
+  <xr:revisionPtr revIDLastSave="767" documentId="13_ncr:1_{2553158B-2B48-A74E-A5FA-9C19D0295F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75693E94-3A19-4A9D-AC3E-E004B9BF1C35}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="translations" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="stroomdiagram Verificatie" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">translations!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">translations!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="87">
   <si>
     <t>ConceptID_2017</t>
   </si>
@@ -247,12 +247,6 @@
 Als GeverifieerdBij == Gevolmachtigde dan AfspraakPartij = verwijzing naar Contactpersoon met rol == Wettelijke vertegenwoordiger
 Als GeverifieerdBij == OTH dan AfspraakPartij = verwijzing naar Contactpersoon; rol en relatie Contactpersoon afleiden uit vrije tekst behorend bij OTH
 Zie Verificatie voor de situatie met meerdere voorkomens van Verificatie.</t>
-  </si>
-  <si>
-    <t>NL-CM:0.0.14</t>
-  </si>
-  <si>
-    <t>DatumTijd (Basiselementen)</t>
   </si>
   <si>
     <t>ZibName 2017</t>
@@ -458,7 +452,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -466,7 +460,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2245,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="40.6640625" customWidth="1"/>
@@ -2260,7 +2253,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2275,7 +2268,7 @@
         <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -2287,13 +2280,13 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2333,7 +2326,7 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K3" t="s">
         <v>66</v>
@@ -2385,7 +2378,7 @@
         <v>67</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="71.400000000000006">
@@ -2410,11 +2403,11 @@
       <c r="H6" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>84</v>
+      <c r="J6" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="K6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2422,75 +2415,80 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" ht="144">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
         <v>61</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" t="s">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="144">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>57</v>
@@ -2499,19 +2497,16 @@
         <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2519,10 +2514,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
         <v>57</v>
@@ -2531,27 +2526,24 @@
         <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" ht="57.6">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>57</v>
@@ -2560,41 +2552,44 @@
         <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="57.6">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2603,10 +2598,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
         <v>59</v>
@@ -2615,45 +2610,36 @@
         <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>6</v>
-      </c>
-      <c r="J13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
       <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" t="s">
-        <v>65</v>
+        <v>51</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2664,16 +2650,16 @@
         <v>61</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" t="s">
         <v>66</v>
       </c>
-      <c r="K15" t="s">
-        <v>79</v>
+      <c r="K15" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2684,70 +2670,50 @@
         <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
-        <v>53</v>
-      </c>
-      <c r="J16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>66</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" ht="57.6">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>62</v>
+      </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>57</v>
       </c>
       <c r="F17" t="s">
         <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H17" t="s">
-        <v>54</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="57.6">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" t="s">
-        <v>55</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="E2:F19">
+  <autoFilter ref="A1:K12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="E2:F18">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"groen: geen wijzigingen"</formula>
     </cfRule>
@@ -2775,15 +2741,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" t="s">
         <v>85</v>
-      </c>
-      <c r="B1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -2800,11 +2766,11 @@
   <dimension ref="B32:F32"/>
   <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="89.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="6" customWidth="1"/>
-    <col min="5" max="6" width="10.88671875" style="6"/>
-    <col min="7" max="16384" width="10.88671875" style="5"/>
+    <col min="1" max="1" width="89.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="5" customWidth="1"/>
+    <col min="5" max="6" width="10.88671875" style="5"/>
+    <col min="7" max="16384" width="10.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="32" ht="22.35" customHeight="1"/>
